--- a/config/demo/forms/app/ncd_hypertension_referral.xlsx
+++ b/config/demo/forms/app/ncd_hypertension_referral.xlsx
@@ -339,7 +339,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:J34"/>
+  <dimension ref="A1:J35"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.59765625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <sheetData>
     <row r="1" ht="15" customHeight="1" s="1">
@@ -480,29 +480,29 @@
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" s="1">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>calculate</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>form_start_timestamp</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>once(if(${_id} != '', now(), ''))</t>
         </is>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1" s="1">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>hidden</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>form_sync_timestamp</t>
         </is>
@@ -934,19 +934,36 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>calculate</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>form_submit_timestamp</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>now()</t>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>form_submit_timestamp_iso</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>format-date-time(now(), '%Y-%m-%dT%H:%M:%S+05:30')</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>calculate</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>form_submit_timestamp_display</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>format-date-time(now(), '%e-%b-%Y %H:%M:%S')</t>
         </is>
       </c>
     </row>

--- a/config/demo/forms/app/ncd_hypertension_referral.xlsx
+++ b/config/demo/forms/app/ncd_hypertension_referral.xlsx
@@ -339,7 +339,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:J35"/>
+  <dimension ref="A1:J34"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.59765625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <sheetData>
     <row r="1" ht="15" customHeight="1" s="1">
@@ -499,34 +499,34 @@
     <row r="8" ht="15" customHeight="1" s="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>hidden</t>
+          <t>begin group</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>form_sync_timestamp</t>
+          <t>inputs</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Patient &amp; CHW Info</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>field-list</t>
         </is>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" s="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>begin group</t>
+          <t>hidden</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>inputs</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>Patient &amp; CHW Info</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>field-list</t>
+          <t>source</t>
         </is>
       </c>
     </row>
@@ -538,31 +538,31 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>source</t>
+          <t>source_id</t>
         </is>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" s="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>hidden</t>
+          <t>begin group</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>source_id</t>
+          <t>user</t>
         </is>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1" s="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>begin group</t>
+          <t>hidden</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>user</t>
+          <t>name</t>
         </is>
       </c>
     </row>
@@ -574,43 +574,58 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>phone</t>
         </is>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1" s="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>hidden</t>
+          <t>end group</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>user</t>
         </is>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1" s="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>end group</t>
+          <t>begin group</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>user</t>
+          <t>contact</t>
         </is>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1" s="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>begin group</t>
+          <t>string</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>contact</t>
+          <t>_id</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Patient's Name</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>select-contact type-person role-patient</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
         </is>
       </c>
     </row>
@@ -622,22 +637,17 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>_id</t>
+          <t>patient_id</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Patient's Name</t>
+          <t>Medic ID</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>select-contact type-person role-patient</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>true</t>
+          <t>hidden</t>
         </is>
       </c>
     </row>
@@ -649,12 +659,12 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>patient_id</t>
+          <t>name</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Medic ID</t>
+          <t>Patient Name</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -666,34 +676,24 @@
     <row r="19" ht="15" customHeight="1" s="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>end group</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>Patient Name</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>hidden</t>
+          <t>contact</t>
         </is>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1" s="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>end group</t>
+          <t>hidden</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>contact</t>
+          <t>t_systolic</t>
         </is>
       </c>
     </row>
@@ -705,70 +705,80 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>t_systolic</t>
+          <t>t_diastolic</t>
         </is>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1" s="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>hidden</t>
+          <t>end group</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>t_diastolic</t>
+          <t>inputs</t>
         </is>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1" s="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>end group</t>
+          <t>begin group</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>inputs</t>
+          <t>referral</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Severe Hypertension Referral</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>field-list</t>
         </is>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1" s="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>begin group</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>referral</t>
+          <t>bp_note</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Severe Hypertension Referral</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>field-list</t>
+          <t>**Previous BP Reading:** ${t_systolic} / ${t_diastolic} mmHg</t>
         </is>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1" s="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one yes_no</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>bp_note</t>
+          <t>phc_visited</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>**Previous BP Reading:** ${t_systolic} / ${t_diastolic} mmHg</t>
+          <t>Did the patient visit the PHC?</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -780,93 +790,88 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>phc_visited</t>
+          <t>willing_to_visit</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Did the patient visit the PHC?</t>
+          <t>Is the patient willing to visit the PHC?</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>${phc_visited} = 'no'</t>
         </is>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1" s="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>select_one yes_no</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>willing_to_visit</t>
+          <t>not_willing_note</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Is the patient willing to visit the PHC?</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
+          <t>Patient is not willing to visit PHC.</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>${phc_visited} = 'no'</t>
+          <t>${phc_visited} = 'no' and ${willing_to_visit} = 'no'</t>
         </is>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1" s="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>not_willing_note</t>
+          <t>phc_visit_date</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Patient is not willing to visit PHC.</t>
+          <t>When will the patient visit the PHC?</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>${phc_visited} = 'no' and ${willing_to_visit} = 'no'</t>
+          <t>${phc_visited} = 'no' and ${willing_to_visit} = 'yes'</t>
         </is>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1" s="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>phc_visit_date</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>When will the patient visit the PHC?</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>${phc_visited} = 'no' and ${willing_to_visit} = 'yes'</t>
+          <t>t_phc_visited</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>${phc_visited}</t>
         </is>
       </c>
     </row>
@@ -878,12 +883,12 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>t_phc_visited</t>
+          <t>t_willing_to_visit</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>${phc_visited}</t>
+          <t>${willing_to_visit}</t>
         </is>
       </c>
     </row>
@@ -895,41 +900,41 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>t_willing_to_visit</t>
+          <t>t_phc_visit_date</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>${willing_to_visit}</t>
+          <t>${phc_visit_date}</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>calculate</t>
+          <t>end group</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>t_phc_visit_date</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>${phc_visit_date}</t>
+          <t>referral</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>end group</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>referral</t>
+          <t>form_submit_timestamp_iso</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>format-date-time(now(), '%Y-%m-%dT%H:%M:%S+05:30')</t>
         </is>
       </c>
     </row>
@@ -941,27 +946,10 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>form_submit_timestamp_iso</t>
+          <t>form_submit_timestamp_display</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>format-date-time(now(), '%Y-%m-%dT%H:%M:%S+05:30')</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>calculate</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>form_submit_timestamp_display</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>format-date-time(now(), '%e-%b-%Y %H:%M:%S')</t>
         </is>

--- a/config/demo/forms/app/ncd_hypertension_referral.xlsx
+++ b/config/demo/forms/app/ncd_hypertension_referral.xlsx
@@ -620,7 +620,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>select-contact type-person role-patient</t>
+          <t>select-contact type-patient</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">

--- a/config/demo/forms/app/ncd_hypertension_referral.xlsx
+++ b/config/demo/forms/app/ncd_hypertension_referral.xlsx
@@ -339,7 +339,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:J34"/>
+  <dimension ref="A1:M34"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.59765625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <sheetData>
     <row r="1" ht="15" customHeight="1" s="1">
@@ -393,6 +393,21 @@
           <t>readonly</t>
         </is>
       </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>constraint</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>constraint_message</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="15" customHeight="1" s="1">
       <c r="A2" s="2" t="inlineStr">
@@ -855,6 +870,21 @@
       <c r="H28" s="2" t="inlineStr">
         <is>
           <t>${phc_visited} = 'no' and ${willing_to_visit} = 'yes'</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>. &gt;= today()</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>Please select today or a future date.</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>today()</t>
         </is>
       </c>
     </row>

--- a/config/demo/forms/app/ncd_hypertension_referral.xlsx
+++ b/config/demo/forms/app/ncd_hypertension_referral.xlsx
@@ -339,7 +339,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:M34"/>
+  <dimension ref="A1:M36"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.59765625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <sheetData>
     <row r="1" ht="15" customHeight="1" s="1">
@@ -393,17 +393,17 @@
           <t>readonly</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="2" t="inlineStr">
         <is>
           <t>constraint</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="2" t="inlineStr">
         <is>
           <t>constraint_message</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="2" t="inlineStr">
         <is>
           <t>default</t>
         </is>
@@ -727,139 +727,119 @@
     <row r="22" ht="15" customHeight="1" s="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>end group</t>
+          <t>hidden</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>inputs</t>
+          <t>t_referral_facility</t>
         </is>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1" s="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>begin group</t>
+          <t>end group</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>referral</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>Severe Hypertension Referral</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>field-list</t>
+          <t>inputs</t>
         </is>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1" s="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>bp_note</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>**Previous BP Reading:** ${t_systolic} / ${t_diastolic} mmHg</t>
+          <t>facility_label</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>if(${t_referral_facility} = 'phc', 'Primary Health Center', if(${t_referral_facility} = 'chc', 'Community Health Center', if(${t_referral_facility} = 'dh', 'District Hospital', 'PHC')))</t>
         </is>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1" s="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>select_one yes_no</t>
+          <t>begin group</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>phc_visited</t>
+          <t>referral</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Did the patient visit the PHC?</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
+          <t>Hypertension ${facility_label} Referral</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>field-list</t>
         </is>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1" s="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>select_one yes_no</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>willing_to_visit</t>
+          <t>bp_note</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Is the patient willing to visit the PHC?</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>${phc_visited} = 'no'</t>
+          <t>**Previous BP Reading:** ${t_systolic} / ${t_diastolic} mmHg</t>
         </is>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1" s="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one yes_no</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>not_willing_note</t>
+          <t>phc_visited</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Patient is not willing to visit PHC.</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>${phc_visited} = 'no' and ${willing_to_visit} = 'no'</t>
+          <t>Did the patient visit the ${facility_label}?</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1" s="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_one yes_no</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>phc_visit_date</t>
+          <t>willing_to_visit</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>When will the patient visit the PHC?</t>
+          <t>Is the patient willing to visit the ${facility_label}?</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -869,56 +849,71 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>${phc_visited} = 'no' and ${willing_to_visit} = 'yes'</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>. &gt;= today()</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>Please select today or a future date.</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>today()</t>
+          <t>${phc_visited} = 'no'</t>
         </is>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1" s="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>calculate</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>t_phc_visited</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>${phc_visited}</t>
+          <t>not_willing_note</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Patient is not willing to visit ${facility_label}.</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>${phc_visited} = 'no' and ${willing_to_visit} = 'no'</t>
         </is>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1" s="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>calculate</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>t_willing_to_visit</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>${willing_to_visit}</t>
+          <t>phc_visit_date</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>When will the patient visit the ${facility_label}?</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>${phc_visited} = 'no' and ${willing_to_visit} = 'yes'</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>. &gt;= today()</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>Please select today or a future date.</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>today()</t>
         </is>
       </c>
     </row>
@@ -930,24 +925,29 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>t_phc_visit_date</t>
+          <t>t_phc_visited</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>${phc_visit_date}</t>
+          <t>${phc_visited}</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>end group</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>referral</t>
+          <t>t_willing_to_visit</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>${willing_to_visit}</t>
         </is>
       </c>
     </row>
@@ -959,27 +959,56 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>form_submit_timestamp_iso</t>
+          <t>t_phc_visit_date</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>format-date-time(now(), '%Y-%m-%dT%H:%M:%S+05:30')</t>
+          <t>${phc_visit_date}</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>end group</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>referral</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
           <t>calculate</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>form_submit_timestamp_iso</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>format-date-time(now(), '%Y-%m-%dT%H:%M:%S+05:30')</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>calculate</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>form_submit_timestamp_display</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>format-date-time(now(), '%e-%b-%Y %H:%M:%S')</t>
         </is>
@@ -998,7 +1027,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.59765625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <sheetData>
     <row r="1" ht="15" customHeight="1" s="1">
@@ -1049,6 +1078,57 @@
       <c r="C3" s="2" t="inlineStr">
         <is>
           <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>ncd_referral_facility</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>phc</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Primary Health Center</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>ncd_referral_facility</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>chc</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Community Health Center</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>ncd_referral_facility</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>dh</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>District Hospital</t>
         </is>
       </c>
     </row>

--- a/config/demo/forms/app/ncd_hypertension_referral.xlsx
+++ b/config/demo/forms/app/ncd_hypertension_referral.xlsx
@@ -339,7 +339,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:M36"/>
+  <dimension ref="M1:M37"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.59765625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <sheetData>
     <row r="1" ht="15" customHeight="1" s="1">
@@ -557,27 +557,27 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" s="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>begin group</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>user</t>
+    <row r="11" ht="15" customHeight="1" s="9">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>ncd_source_id</t>
         </is>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1" s="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>hidden</t>
+          <t>begin group</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>user</t>
         </is>
       </c>
     </row>
@@ -589,58 +589,43 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>name</t>
         </is>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1" s="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>end group</t>
+          <t>hidden</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>user</t>
+          <t>phone</t>
         </is>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1" s="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>begin group</t>
+          <t>end group</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>contact</t>
+          <t>user</t>
         </is>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1" s="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>begin group</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>_id</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>Patient's Name</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>select-contact type-patient</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>true</t>
+          <t>contact</t>
         </is>
       </c>
     </row>
@@ -652,17 +637,22 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>patient_id</t>
+          <t>_id</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Medic ID</t>
+          <t>Patient's Name</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>hidden</t>
+          <t>select-contact type-patient</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
         </is>
       </c>
     </row>
@@ -674,12 +664,12 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>patient_id</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Patient Name</t>
+          <t>Medic ID</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -691,24 +681,34 @@
     <row r="19" ht="15" customHeight="1" s="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>end group</t>
+          <t>string</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>contact</t>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Patient Name</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>hidden</t>
         </is>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1" s="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>hidden</t>
+          <t>end group</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>t_systolic</t>
+          <t>contact</t>
         </is>
       </c>
     </row>
@@ -720,7 +720,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>t_diastolic</t>
+          <t>t_systolic</t>
         </is>
       </c>
     </row>
@@ -732,97 +732,87 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>t_referral_facility</t>
+          <t>t_diastolic</t>
         </is>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1" s="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>end group</t>
+          <t>hidden</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>inputs</t>
+          <t>t_referral_facility</t>
         </is>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1" s="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>calculate</t>
+          <t>end group</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>facility_label</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>if(${t_referral_facility} = 'phc', 'Primary Health Center', if(${t_referral_facility} = 'chc', 'Community Health Center', if(${t_referral_facility} = 'dh', 'District Hospital', 'PHC')))</t>
+          <t>inputs</t>
         </is>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1" s="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>begin group</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>referral</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>Hypertension ${facility_label} Referral</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>field-list</t>
+          <t>facility_label</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>if(${t_referral_facility} = 'phc', 'Primary Health Center', if(${t_referral_facility} = 'chc', 'Community Health Center', if(${t_referral_facility} = 'dh', 'District Hospital', 'PHC')))</t>
         </is>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1" s="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>begin group</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>bp_note</t>
+          <t>referral</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>**Previous BP Reading:** ${t_systolic} / ${t_diastolic} mmHg</t>
+          <t>Hypertension ${facility_label} Referral</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>field-list</t>
         </is>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1" s="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>select_one yes_no</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>phc_visited</t>
+          <t>bp_note</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Did the patient visit the ${facility_label}?</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
+          <t>**Previous BP Reading:** ${t_systolic} / ${t_diastolic} mmHg</t>
         </is>
       </c>
     </row>
@@ -834,120 +824,125 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>willing_to_visit</t>
+          <t>phc_visited</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Is the patient willing to visit the ${facility_label}?</t>
+          <t>Did the patient visit the ${facility_label}?</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
           <t>yes</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>${phc_visited} = 'no'</t>
         </is>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1" s="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one yes_no</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>not_willing_note</t>
+          <t>willing_to_visit</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Patient is not willing to visit ${facility_label}.</t>
+          <t>Is the patient willing to visit the ${facility_label}?</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>${phc_visited} = 'no' and ${willing_to_visit} = 'no'</t>
+          <t>${phc_visited} = 'no'</t>
         </is>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1" s="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>phc_visit_date</t>
+          <t>not_willing_note</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>When will the patient visit the ${facility_label}?</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
+          <t>Patient is not willing to visit ${facility_label}.</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>${phc_visited} = 'no' and ${willing_to_visit} = 'yes'</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>. &gt;= today()</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>Please select today or a future date.</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>today()</t>
+          <t>${phc_visited} = 'no' and ${willing_to_visit} = 'no'</t>
         </is>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1" s="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>phc_visit_date</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>When will the patient visit the ${facility_label}?</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>${phc_visited} = 'no' and ${willing_to_visit} = 'yes'</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>. &gt;= today()</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>Please select today or a future date.</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>today()</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="15" customHeight="1" s="1">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
           <t>calculate</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>t_phc_visited</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>${phc_visited}</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>calculate</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>t_willing_to_visit</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>${willing_to_visit}</t>
         </is>
       </c>
     </row>
@@ -959,41 +954,41 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>t_phc_visit_date</t>
+          <t>t_willing_to_visit</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>${phc_visit_date}</t>
+          <t>${willing_to_visit}</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>end group</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>referral</t>
+          <t>t_phc_visit_date</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>${phc_visit_date}</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>calculate</t>
+          <t>end group</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>form_submit_timestamp_iso</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>format-date-time(now(), '%Y-%m-%dT%H:%M:%S+05:30')</t>
+          <t>referral</t>
         </is>
       </c>
     </row>
@@ -1005,10 +1000,27 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
+          <t>form_submit_timestamp_iso</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>format-date-time(now(), '%Y-%m-%dT%H:%M:%S+05:30')</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>calculate</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>form_submit_timestamp_display</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>format-date-time(now(), '%e-%b-%Y %H:%M:%S')</t>
         </is>
